--- a/lead_generation_forms/028_lead_generation_form--lead_generation_forms.xlsx
+++ b/lead_generation_forms/028_lead_generation_form--lead_generation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1093,34 +1093,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>lead_generation_form_industry_choices</t>
+          <t>lead_generation_form_lead_source_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>marketing</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>lead_generation_form_industry_choices</t>
+          <t>lead_generation_form_lead_source_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>online_ad</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Online Ad</t>
         </is>
       </c>
     </row>
@@ -1132,46 +1132,46 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Social Media</t>
+          <t>Referral</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lead_generation_form_lead_source_choices</t>
+          <t>lead_generation_form_agency_services_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>online_ad</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Online Ad</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>lead_generation_form_lead_source_choices</t>
+          <t>lead_generation_form_agency_services_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>referral</t>
+          <t>advertising</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Referral</t>
+          <t>Advertising</t>
         </is>
       </c>
     </row>
@@ -1183,46 +1183,46 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>marketing</t>
+          <t>design</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Design</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>lead_generation_form_agency_services_choices</t>
+          <t>lead_generation_form_company_size_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>advertising</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Advertising</t>
+          <t>1-10</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>lead_generation_form_agency_services_choices</t>
+          <t>lead_generation_form_company_size_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>11-50</t>
         </is>
       </c>
     </row>
@@ -1234,46 +1234,46 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>51-100</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>51-100</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>lead_generation_form_company_size_choices</t>
+          <t>lead_generation_form_industry_experience_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>11-50</t>
+          <t>0-2_years</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>11-50</t>
+          <t>0-2 years</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>lead_generation_form_company_size_choices</t>
+          <t>lead_generation_form_industry_experience_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>51-100</t>
+          <t>2-5_years</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>51-100</t>
+          <t>2-5 years</t>
         </is>
       </c>
     </row>
@@ -1285,78 +1285,44 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0-2_years</t>
+          <t>5+_years</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0-2 years</t>
+          <t>5+ years</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>lead_generation_form_industry_experience_choices</t>
+          <t>lead_generation_form_lead_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2-5_years</t>
+          <t>lead_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2-5 years</t>
+          <t>Lead 1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>lead_generation_form_industry_experience_choices</t>
+          <t>lead_generation_form_lead_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5+_years</t>
+          <t>lead_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
-        <is>
-          <t>5+ years</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>lead_generation_form_lead_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>lead_1</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Lead 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>lead_generation_form_lead_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>lead_2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
         <is>
           <t>Lead 2</t>
         </is>
